--- a/語憶/112年至114年花東市區客運搭車定期票/112年至114年花東市區客運搭車定期票.xlsx
+++ b/語憶/112年至114年花東市區客運搭車定期票/112年至114年花東市區客運搭車定期票.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9bfbd26f7bb2cad2/桌面/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{FA22D7B0-9214-492B-9885-2182E7FFCBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD61A0F9-F720-4647-A943-F9151A5F3BAB}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{FA22D7B0-9214-492B-9885-2182E7FFCBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{225C7915-F387-46D1-A1ED-FCA4A72DF432}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2F39B4FA-82F6-4E47-A028-E5A5E51F61D8}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{2F39B4FA-82F6-4E47-A028-E5A5E51F61D8}"/>
   </bookViews>
   <sheets>
     <sheet name="112年至114年花東市區客運搭車定期票統計表" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
   <si>
     <t>113年成長率</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -125,7 +125,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -193,13 +193,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -233,23 +285,50 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -589,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075C44BC-8D21-42D4-86EE-933A3CEBB9A4}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="6" width="14.6328125" customWidth="1"/>
@@ -628,29 +707,29 @@
       <c r="D2" s="6">
         <v>13203</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E2" s="18">
         <v>4.0655999999999999</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="20">
         <v>0.42580000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A3" s="16"/>
+      <c r="A3" s="17"/>
       <c r="B3" s="7">
-        <v>3.3999999999999998E-3</v>
+        <v>4.3E-3</v>
       </c>
       <c r="C3" s="7">
-        <v>1.77E-2</v>
-      </c>
-      <c r="D3" s="8">
-        <v>2.7199999999999998E-2</v>
-      </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="14"/>
+        <v>2.46E-2</v>
+      </c>
+      <c r="D3" s="9">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="22" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="5">
@@ -662,146 +741,240 @@
       <c r="D4" s="6">
         <v>85367</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="18">
         <v>2.8780999999999999</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="20">
         <v>0.80359999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="15"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="7">
-        <v>2.2800000000000001E-2</v>
+        <v>2.8899999999999999E-2</v>
       </c>
       <c r="C5" s="7">
-        <v>9.0300000000000005E-2</v>
+        <v>0.12570000000000001</v>
       </c>
       <c r="D5" s="9">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+        <v>0.26140000000000002</v>
+      </c>
+      <c r="E5" s="19"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="5">
+        <v>407688</v>
+      </c>
+      <c r="C6" s="5">
+        <v>319815</v>
+      </c>
+      <c r="D6" s="6">
+        <v>228013</v>
+      </c>
+      <c r="E6" s="18">
+        <v>-0.2155</v>
+      </c>
+      <c r="F6" s="20">
+        <v>-0.28699999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A7" s="23"/>
+      <c r="B7" s="7">
+        <v>0.9667</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.84970000000000001</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0.69820000000000004</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="21"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A8" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="5">
+        <v>421721</v>
+      </c>
+      <c r="C8" s="5">
+        <v>376407</v>
+      </c>
+      <c r="D8" s="6">
+        <v>326583</v>
+      </c>
+      <c r="E8" s="18">
+        <v>-0.1075</v>
+      </c>
+      <c r="F8" s="20">
+        <v>-0.13239999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A9" s="25"/>
+      <c r="B9" s="10">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="C9" s="10">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="12" spans="1:6" ht="37" x14ac:dyDescent="0.4">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="2">
+        <v>112</v>
+      </c>
+      <c r="C12" s="2">
+        <v>113</v>
+      </c>
+      <c r="D12" s="3">
+        <v>114</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B13" s="5">
         <v>4071</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C13" s="5">
         <v>20893</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D13" s="6">
         <v>29947</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E13" s="11">
         <v>4.1322000000000001</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F13" s="12">
         <v>0.43340000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A7" s="15"/>
-      <c r="B7" s="10">
-        <v>7.6E-3</v>
-      </c>
-      <c r="C7" s="10">
-        <v>3.9899999999999998E-2</v>
-      </c>
-      <c r="D7" s="9">
-        <v>6.1800000000000001E-2</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
-    </row>
-    <row r="8" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A8" s="15" t="s">
+    <row r="14" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A14" s="13"/>
+      <c r="B14" s="7">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="C14" s="7">
+        <v>0.14149999999999999</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0.18909999999999999</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A15" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5">
-        <v>517195</v>
-      </c>
-      <c r="C8" s="5">
-        <v>446558</v>
-      </c>
-      <c r="D8" s="6">
-        <v>356411</v>
-      </c>
-      <c r="E8" s="13">
-        <v>-0.1366</v>
-      </c>
-      <c r="F8" s="14">
-        <v>-0.2019</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A9" s="15"/>
-      <c r="B9" s="7">
-        <v>0.96619999999999995</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0.85209999999999997</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0.73499999999999999</v>
-      </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
-    </row>
-    <row r="10" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A10" s="11" t="s">
+      <c r="B15" s="5">
+        <v>109507</v>
+      </c>
+      <c r="C15" s="5">
+        <v>126743</v>
+      </c>
+      <c r="D15" s="6">
+        <v>128398</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0.15740000000000001</v>
+      </c>
+      <c r="F15" s="12">
+        <v>1.3100000000000001E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A16" s="13"/>
+      <c r="B16" s="7">
+        <v>0.96419999999999995</v>
+      </c>
+      <c r="C16" s="7">
+        <v>0.85850000000000004</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0.81089999999999995</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+    </row>
+    <row r="17" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A17" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="5">
-        <v>535299</v>
-      </c>
-      <c r="C10" s="5">
-        <v>524043</v>
-      </c>
-      <c r="D10" s="6">
-        <v>484928</v>
-      </c>
-      <c r="E10" s="13">
-        <v>-2.1000000000000001E-2</v>
-      </c>
-      <c r="F10" s="14">
-        <v>-7.46E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
-      <c r="A11" s="12"/>
-      <c r="B11" s="10">
+      <c r="B17" s="5">
+        <v>113578</v>
+      </c>
+      <c r="C17" s="5">
+        <v>147636</v>
+      </c>
+      <c r="D17" s="6">
+        <v>158345</v>
+      </c>
+      <c r="E17" s="11">
+        <v>0.2999</v>
+      </c>
+      <c r="F17" s="12">
+        <v>7.2499999999999995E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18.5" x14ac:dyDescent="0.4">
+      <c r="A18" s="15"/>
+      <c r="B18" s="10">
         <v>1</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C18" s="10">
         <v>1</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D18" s="8">
         <v>1</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="21">
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
